--- a/f1_scores new.xlsx
+++ b/f1_scores new.xlsx
@@ -571,7 +571,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="8"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="7"/>
@@ -580,7 +580,6 @@
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="18"/>
     <xf numFmtId="0" fontId="17" fillId="13" borderId="0" xfId="22"/>
     <xf numFmtId="0" fontId="17" fillId="21" borderId="0" xfId="30"/>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" xfId="38"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="6" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
@@ -1106,27 +1105,27 @@
       <c r="D9" s="4">
         <v>0</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="3">
         <v>94.68</v>
       </c>
       <c r="F9" s="3">
         <v>93.95</v>
       </c>
-      <c r="G9" s="8">
-        <v>94.79</v>
+      <c r="G9" s="3">
+        <v>94.024000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="8">
         <v>89.37</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="8">
         <v>89.17</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="8">
         <v>88.53</v>
       </c>
       <c r="E10" s="3">
